--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84C435F-F790-6A44-9928-65DA6E562E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85E444-0AF7-414F-ACF0-F8564AB813A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Laminar" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$E$10</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="8">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -882,4 +883,71 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6391877-51E4-D242-9782-E0B87465A1CE}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <f>A4</f>
+        <v>166.33333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <f>B1-B2</f>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1">
+        <f>E1-1-E2</f>
+        <v>332.66666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <f>((E1-1)*(1/(1+B2/B3)))</f>
+        <v>166.33333333333331</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A85E444-0AF7-414F-ACF0-F8564AB813A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD156EE-1B1B-4D43-8E57-E7A972E0FFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="660" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -919,7 +919,7 @@
       </c>
       <c r="E2" s="1">
         <f>A4</f>
-        <v>166.33333333333331</v>
+        <v>277.22222222222223</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -928,7 +928,7 @@
       </c>
       <c r="B3">
         <f>B1-B2</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -938,13 +938,13 @@
       </c>
       <c r="E3" s="1">
         <f>E1-1-E2</f>
-        <v>332.66666666666669</v>
+        <v>221.77777777777777</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>((E1-1)*(1/(1+B2/B3)))</f>
-        <v>166.33333333333331</v>
+        <v>277.22222222222223</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD156EE-1B1B-4D43-8E57-E7A972E0FFB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263B4544-9199-4048-94D6-FABD3432684B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="9">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -89,6 +89,9 @@
   <si>
     <t>N_E</t>
   </si>
+  <si>
+    <t>LAMINAR</t>
+  </si>
 </sst>
 </file>
 
@@ -110,12 +113,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -130,11 +145,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,7 +904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6391877-51E4-D242-9782-E0B87465A1CE}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -895,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -919,7 +936,7 @@
       </c>
       <c r="E2" s="1">
         <f>A4</f>
-        <v>277.22222222222223</v>
+        <v>399.20000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -928,7 +945,7 @@
       </c>
       <c r="B3">
         <f>B1-B2</f>
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -938,14 +955,282 @@
       </c>
       <c r="E3" s="1">
         <f>E1-1-E2</f>
-        <v>221.77777777777777</v>
+        <v>99.799999999999955</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>((E1-1)*(1/(1+B2/B3)))</f>
-        <v>277.22222222222223</v>
-      </c>
+        <v>399.20000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <f>A11</f>
+        <v>249.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <f>B8-B9</f>
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <f>E8-A11-1</f>
+        <v>249.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <f>((E8-1)*(1/(1+B9/B10)))</f>
+        <v>249.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="3">
+        <f>A17</f>
+        <v>199.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2">
+        <f>B14-B15</f>
+        <v>30</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3">
+        <f>E14-A17-2</f>
+        <v>198.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <f>((E14-1)*(1/(1+B15/B16)))</f>
+        <v>199.5</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2">
+        <v>60</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2">
+        <v>30</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3">
+        <f>A23</f>
+        <v>149.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2">
+        <f>B20-B21</f>
+        <v>30</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3">
+        <f>E20-A23-2</f>
+        <v>148.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <f>((E20-1)*(1/(1+B21/B22)))</f>
+        <v>149.5</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="2">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="2">
+        <v>30</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3">
+        <f>A29</f>
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2">
+        <f>B26-B27</f>
+        <v>30</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3">
+        <f>E26-A29-2</f>
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <f>((E26-1)*(1/(1+B27/B28)))</f>
+        <v>49.5</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263B4544-9199-4048-94D6-FABD3432684B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0423F402-34FA-7741-8C27-9F8F3CD6CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="13">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -92,6 +92,18 @@
   <si>
     <t>LAMINAR</t>
   </si>
+  <si>
+    <t>Dispersion</t>
+  </si>
+  <si>
+    <t>unified</t>
+  </si>
+  <si>
+    <t>Laminar</t>
+  </si>
+  <si>
+    <t>Adler Hovarko</t>
+  </si>
 </sst>
 </file>
 
@@ -113,7 +125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +144,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -145,13 +163,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,10 +923,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6391877-51E4-D242-9782-E0B87465A1CE}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="10.83203125" style="6"/>
+    <col min="12" max="12" width="10.83203125" style="6"/>
+    <col min="18" max="18" width="10.83203125" style="6"/>
+    <col min="19" max="19" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" style="6"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -924,7 +950,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -939,7 +965,7 @@
         <v>399.20000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -958,23 +984,50 @@
         <v>99.799999999999955</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>((E1-1)*(1/(1+B2/B3)))</f>
         <v>399.20000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>500</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="5">
+        <v>500</v>
+      </c>
+      <c r="G7" s="5">
+        <v>500</v>
+      </c>
+      <c r="M7" s="5">
+        <v>500</v>
+      </c>
+      <c r="S7">
+        <v>200</v>
+      </c>
+      <c r="Y7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -990,8 +1043,68 @@
       <c r="E8">
         <v>500</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>500</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8">
+        <v>500</v>
+      </c>
+      <c r="S8" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>45</v>
+      </c>
+      <c r="U8" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" t="s">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>200</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>100</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -1005,8 +1118,60 @@
         <f>A11</f>
         <v>249.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>30</v>
+      </c>
+      <c r="J9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1">
+        <f>G11</f>
+        <v>349.29999999999995</v>
+      </c>
+      <c r="M9" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>20</v>
+      </c>
+      <c r="P9" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="1">
+        <f>M11</f>
+        <v>277.22222222222223</v>
+      </c>
+      <c r="S9" t="s">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>25</v>
+      </c>
+      <c r="V9" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" s="1">
+        <f>S11</f>
+        <v>88.444444444444443</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z9">
+        <v>40</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="1">
+        <f>Y11</f>
+        <v>119.40000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1021,22 +1186,106 @@
         <v>7</v>
       </c>
       <c r="E10" s="1">
-        <f>E8-A11-1</f>
-        <v>249.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <f>E8-A11-2</f>
+        <v>248.5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>H8-H9</f>
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <f>K8-G11-1</f>
+        <v>149.70000000000005</v>
+      </c>
+      <c r="M10" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <f>N8-N9</f>
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="1">
+        <f>Q8-M11-1</f>
+        <v>221.77777777777777</v>
+      </c>
+      <c r="S10" t="s">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <f>T8-T9</f>
+        <v>20</v>
+      </c>
+      <c r="U10" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" t="s">
+        <v>7</v>
+      </c>
+      <c r="W10" s="1">
+        <f>W8-S11-1</f>
+        <v>110.55555555555556</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f>Z8-Z9</f>
+        <v>60</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC10" s="1">
+        <f>AC8-Y11-1</f>
+        <v>79.59999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f>((E8-1)*(1/(1+B9/B10)))</f>
         <v>249.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G11" s="1">
+        <f>((K8-1)*(1/(1+H9/H10)))</f>
+        <v>349.29999999999995</v>
+      </c>
+      <c r="M11" s="1">
+        <f>((Q8-1)*(1/(1+N9/N10)))</f>
+        <v>277.22222222222223</v>
+      </c>
+      <c r="S11" s="1">
+        <f>((W8-1)*(1/(1+T9/T10)))</f>
+        <v>88.444444444444443</v>
+      </c>
+      <c r="Y11" s="1">
+        <f>((AC8-1)*(1/(1+Z9/Z10)))</f>
+        <v>119.40000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
@@ -1052,8 +1301,14 @@
       <c r="E14" s="2">
         <v>400</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="M14" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
@@ -1068,8 +1323,38 @@
         <f>A17</f>
         <v>199.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>45</v>
+      </c>
+      <c r="O15" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -1087,8 +1372,34 @@
         <f>E14-A17-2</f>
         <v>198.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>70</v>
+      </c>
+      <c r="J16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <f>G18</f>
+        <v>29.7</v>
+      </c>
+      <c r="M16" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>20</v>
+      </c>
+      <c r="P16" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>M18</f>
+        <v>166.11111111111111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <f>((E14-1)*(1/(1+B15/B16)))</f>
         <v>199.5</v>
@@ -1097,13 +1408,57 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <f>H15-H16</f>
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1">
+        <f>K15-G18-1</f>
+        <v>69.3</v>
+      </c>
+      <c r="M17" t="s">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f>N15-N16</f>
+        <v>25</v>
+      </c>
+      <c r="O17" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="1">
+        <f>Q15-M18-1</f>
+        <v>132.88888888888889</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G18" s="1">
+        <f>((K15-1)*(1/(1+H16/H17)))</f>
+        <v>29.7</v>
+      </c>
+      <c r="M18" s="1">
+        <f>((Q15-1)*(1/(1+N16/N17)))</f>
+        <v>166.11111111111111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -1119,8 +1474,14 @@
       <c r="E20" s="2">
         <v>300</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>300</v>
+      </c>
+      <c r="M20" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
@@ -1135,8 +1496,38 @@
         <f>A23</f>
         <v>149.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21">
+        <v>300</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -1154,8 +1545,34 @@
         <f>E20-A23-2</f>
         <v>148.5</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>50</v>
+      </c>
+      <c r="J22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="1">
+        <f>G24</f>
+        <v>149.5</v>
+      </c>
+      <c r="M22" t="s">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>20</v>
+      </c>
+      <c r="P22" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q22" s="1">
+        <f>M24</f>
+        <v>110.55555555555556</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <f>((E20-1)*(1/(1+B21/B22)))</f>
         <v>149.5</v>
@@ -1164,13 +1581,60 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f>H21-H22</f>
+        <v>50</v>
+      </c>
+      <c r="I23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" t="s">
+        <v>7</v>
+      </c>
+      <c r="K23" s="1">
+        <f>K21-G24-2</f>
+        <v>148.5</v>
+      </c>
+      <c r="M23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f>N21-N22</f>
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="1">
+        <f>Q21-M24-1</f>
+        <v>88.444444444444443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G24" s="1">
+        <f>((K21-1)*(1/(1+H22/H23)))</f>
+        <v>149.5</v>
+      </c>
+      <c r="M24" s="1">
+        <f>((Q21-1)*(1/(1+N22/N23)))</f>
+        <v>110.55555555555556</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
@@ -1184,10 +1648,25 @@
         <v>5</v>
       </c>
       <c r="E26" s="2">
+        <v>200</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="I26" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
@@ -1200,10 +1679,23 @@
       </c>
       <c r="E27" s="3">
         <f>A29</f>
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>99.5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
+      <c r="J27" t="s">
+        <v>6</v>
+      </c>
+      <c r="K27" s="1">
+        <f>G29</f>
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -1219,18 +1711,101 @@
       </c>
       <c r="E28" s="3">
         <f>E26-A29-2</f>
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>98.5</v>
+      </c>
+      <c r="G28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f>H26-H27</f>
+        <v>50</v>
+      </c>
+      <c r="I28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
+        <v>7</v>
+      </c>
+      <c r="K28" s="1">
+        <f>K26-G29-2</f>
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <f>((E26-1)*(1/(1+B27/B28)))</f>
-        <v>49.5</v>
+        <v>99.5</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
+      <c r="G29" s="1">
+        <f>((K26-1)*(1/(1+H27/H28)))</f>
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>200</v>
+      </c>
+      <c r="I32" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="7:11" x14ac:dyDescent="0.2">
+      <c r="G33" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="J33" t="s">
+        <v>6</v>
+      </c>
+      <c r="K33" s="1">
+        <f>G35</f>
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="34" spans="7:11" x14ac:dyDescent="0.2">
+      <c r="G34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f>H32-H33</f>
+        <v>100</v>
+      </c>
+      <c r="I34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" s="1">
+        <f>K32-G35-2</f>
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="35" spans="7:11" x14ac:dyDescent="0.2">
+      <c r="G35" s="1">
+        <f>((K32-1)*(1/(1+H33/H34)))</f>
+        <v>99.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0423F402-34FA-7741-8C27-9F8F3CD6CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8435B800-FE6D-4349-ACB2-45F6D7A8339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="12980" yWindow="500" windowWidth="28800" windowHeight="16460" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="13">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -1746,11 +1746,29 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" s="5">
+        <v>200</v>
+      </c>
       <c r="G31">
         <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>60</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>200</v>
+      </c>
       <c r="G32" t="s">
         <v>1</v>
       </c>
@@ -1767,7 +1785,21 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2">
+        <v>30</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3">
+        <f>A35</f>
+        <v>99.5</v>
+      </c>
       <c r="G33" t="s">
         <v>2</v>
       </c>
@@ -1782,7 +1814,24 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="34" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2">
+        <f>B32-B33</f>
+        <v>30</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="3">
+        <f>E32-A35-2</f>
+        <v>98.5</v>
+      </c>
       <c r="G34" t="s">
         <v>0</v>
       </c>
@@ -1801,7 +1850,15 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="35" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <f>((E32-1)*(1/(1+B33/B34)))</f>
+        <v>99.5</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
       <c r="G35" s="1">
         <f>((K32-1)*(1/(1+H33/H34)))</f>
         <v>99.5</v>

--- a/Data/Data_Scripts_Evaluation/Calculation.xlsx
+++ b/Data/Data_Scripts_Evaluation/Calculation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tuanaoyuncu/Documents/GitHub/nRTD/Data/Data_Scripts_Evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8435B800-FE6D-4349-ACB2-45F6D7A8339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BC0B8E-4DEA-1C45-A508-5174B3207054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12980" yWindow="500" windowWidth="28800" windowHeight="16460" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16400" activeTab="1" xr2:uid="{24048C4F-BF72-8947-858C-9A2227B38C89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="13">
   <si>
     <t>DeltaT_E</t>
   </si>
@@ -923,7 +923,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6391877-51E4-D242-9782-E0B87465A1CE}">
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="10.83203125" style="6"/>
@@ -1307,6 +1307,9 @@
       <c r="M14" s="5">
         <v>300</v>
       </c>
+      <c r="S14">
+        <v>200</v>
+      </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -1353,6 +1356,21 @@
       <c r="Q15">
         <v>300</v>
       </c>
+      <c r="S15" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>45</v>
+      </c>
+      <c r="U15" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15">
+        <v>500</v>
+      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
@@ -1398,8 +1416,21 @@
         <f>M18</f>
         <v>166.11111111111111</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S16" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16">
+        <v>25</v>
+      </c>
+      <c r="V16" t="s">
+        <v>6</v>
+      </c>
+      <c r="W16" s="1">
+        <f>S18</f>
+        <v>221.77777777777777</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <f>((E14-1)*(1/(1+B15/B16)))</f>
         <v>199.5</v>
@@ -1442,8 +1473,25 @@
         <f>Q15-M18-1</f>
         <v>132.88888888888889</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S17" t="s">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <f>T15-T16</f>
+        <v>20</v>
+      </c>
+      <c r="U17" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" t="s">
+        <v>7</v>
+      </c>
+      <c r="W17" s="1">
+        <f>W15-S18-1</f>
+        <v>277.22222222222223</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="G18" s="1">
         <f>((K15-1)*(1/(1+H16/H17)))</f>
         <v>29.7</v>
@@ -1452,13 +1500,17 @@
         <f>((Q15-1)*(1/(1+N16/N17)))</f>
         <v>166.11111111111111</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="1">
+        <f>((W15-1)*(1/(1+T16/T17)))</f>
+        <v>221.77777777777777</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
@@ -1481,7 +1533,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2</v>
       </c>
@@ -1526,8 +1578,11 @@
       <c r="Q21">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S21">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -1571,8 +1626,23 @@
         <f>M24</f>
         <v>110.55555555555556</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S22" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>45</v>
+      </c>
+      <c r="U22" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <f>((E20-1)*(1/(1+B21/B22)))</f>
         <v>149.5</v>
@@ -1615,8 +1685,21 @@
         <f>Q21-M24-1</f>
         <v>88.444444444444443</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S23" t="s">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>25</v>
+      </c>
+      <c r="V23" t="s">
+        <v>6</v>
+      </c>
+      <c r="W23" s="1">
+        <f>S25</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="G24" s="1">
         <f>((K21-1)*(1/(1+H22/H23)))</f>
         <v>149.5</v>
@@ -1625,16 +1708,37 @@
         <f>((Q21-1)*(1/(1+N22/N23)))</f>
         <v>110.55555555555556</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S24" t="s">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f>T22-T23</f>
+        <v>20</v>
+      </c>
+      <c r="U24" t="s">
+        <v>4</v>
+      </c>
+      <c r="V24" t="s">
+        <v>7</v>
+      </c>
+      <c r="W24" s="1">
+        <f>W22-S25-1</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>200</v>
       </c>
       <c r="G25">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S25" s="1">
+        <f>((W22-1)*(1/(1+T23/T24)))</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
@@ -1666,7 +1770,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
@@ -1695,7 +1799,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -1731,7 +1835,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <f>((E26-1)*(1/(1+B27/B28)))</f>
         <v>99.5</v>
@@ -1745,7 +1849,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>200</v>
       </c>
@@ -1753,7 +1857,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1</v>
       </c>
@@ -1864,6 +1968,204 @@
         <v>99.5</v>
       </c>
     </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="5">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2">
+        <v>60</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2">
+        <v>30</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="3">
+        <f>A41</f>
+        <v>166.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2">
+        <f>B38-B39</f>
+        <v>30</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="3">
+        <f>E38-A41-2</f>
+        <v>165.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <f>((E38-1)*(1/(1+B39/B40)))</f>
+        <v>166.5</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" s="2">
+        <v>60</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" s="2">
+        <v>30</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="3">
+        <f>A47</f>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2">
+        <f>B44-B45</f>
+        <v>30</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3">
+        <f>E44-A47-2</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <f>((E44-1)*(1/(1+B45/B46)))</f>
+        <v>83</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="2">
+        <v>60</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="2">
+        <v>30</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3">
+        <f>A52</f>
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2">
+        <f>B49-B50</f>
+        <v>30</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="3">
+        <f>E49-A52-2</f>
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <f>((E49-1)*(1/(1+B50/B51)))</f>
+        <v>41.5</v>
+      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
